--- a/data/trans_dic/P70D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,23</t>
+          <t>3,14; 7,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,63</t>
+          <t>4,31; 10,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,18</t>
+          <t>4,28; 8,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,57</t>
+          <t>1,0; 4,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,97</t>
+          <t>4,52; 8,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,37</t>
+          <t>1,92; 5,39</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,8</t>
+          <t>1,64; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,97</t>
+          <t>1,1; 4,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,11</t>
+          <t>1,64; 4,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,36</t>
+          <t>3,67; 8,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,7</t>
+          <t>4,2; 10,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,4</t>
+          <t>4,63; 8,69</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,92</t>
+          <t>2,56; 5,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,39</t>
+          <t>4,49; 7,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,72</t>
+          <t>3,63; 5,6</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10674; 27257</t>
+          <t>10407; 25958</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11157; 27293</t>
+          <t>11062; 27361</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25545; 48059</t>
+          <t>25134; 47959</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8168; 36827</t>
+          <t>8026; 36109</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18307; 36088</t>
+          <t>18178; 34589</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23579; 64895</t>
+          <t>23143; 65131</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5944; 20730</t>
+          <t>5864; 20015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3305; 12877</t>
+          <t>3583; 13027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11346; 27994</t>
+          <t>11167; 27407</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17721; 39472</t>
+          <t>17346; 39310</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20199; 51392</t>
+          <t>20175; 52350</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44113; 80066</t>
+          <t>44102; 82814</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49777; 96815</t>
+          <t>50276; 101240</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67339; 108218</t>
+          <t>65658; 105418</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125685; 196400</t>
+          <t>124570; 192169</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,84</t>
+          <t>3,33; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,66</t>
+          <t>4,36; 10,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,16</t>
+          <t>4,24; 7,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,48</t>
+          <t>2,38; 5,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,6</t>
+          <t>4,37; 8,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,39</t>
+          <t>3,63; 6,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,6</t>
+          <t>1,31; 4,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,02</t>
+          <t>1,44; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,02</t>
+          <t>1,81; 4,05</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,32</t>
+          <t>3,63; 8,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,9</t>
+          <t>5,71; 10,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,69</t>
+          <t>5,11; 8,23</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,15</t>
+          <t>3,49; 5,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,2</t>
+          <t>4,93; 7,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,6</t>
+          <t>4,35; 5,87</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34799</t>
+          <t>37360</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10407; 25958</t>
+          <t>12129; 30206</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11062; 27361</t>
+          <t>12097; 28618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25134; 47959</t>
+          <t>27238; 50860</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25423</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>51553</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8026; 36109</t>
+          <t>14933; 36374</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18178; 34589</t>
+          <t>19673; 38669</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23143; 65131</t>
+          <t>39096; 65558</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>20957</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5864; 20015</t>
+          <t>5513; 19751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3583; 13027</t>
+          <t>4887; 15300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11167; 27407</t>
+          <t>13792; 30818</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26704</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60686</t>
+          <t>62889</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17346; 39310</t>
+          <t>18806; 42201</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20175; 52350</t>
+          <t>25594; 46306</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44102; 82814</t>
+          <t>49334; 79526</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50276; 101240</t>
+          <t>67463; 104557</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65658; 105418</t>
+          <t>74678; 108319</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124570; 192169</t>
+          <t>149857; 202238</t>
         </is>
       </c>
     </row>
